--- a/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -656,40 +656,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="G7" s="2" t="s">
         <v>3</v>
       </c>
@@ -705,20 +705,23 @@
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>449900</v>
+        <v>447600</v>
       </c>
       <c r="E8" s="3">
-        <v>297000</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
+        <v>438500</v>
+      </c>
+      <c r="F8" s="3">
+        <v>289500</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -735,20 +738,23 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>293100</v>
+        <v>298200</v>
       </c>
       <c r="E9" s="3">
-        <v>192400</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
+        <v>571300</v>
+      </c>
+      <c r="F9" s="3">
+        <v>187500</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -765,20 +771,23 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>156800</v>
+        <v>149500</v>
       </c>
       <c r="E10" s="3">
-        <v>104600</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+        <v>-132800</v>
+      </c>
+      <c r="F10" s="3">
+        <v>101900</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -795,9 +804,12 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,19 +822,20 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>3</v>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,21 +885,24 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>2400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -899,9 +918,12 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -929,9 +951,12 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,19 +966,20 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>393500</v>
+        <v>390400</v>
       </c>
       <c r="E17" s="3">
-        <v>246700</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
+        <v>383600</v>
+      </c>
+      <c r="F17" s="3">
+        <v>240500</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>3</v>
@@ -970,20 +996,23 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>56300</v>
+        <v>57200</v>
       </c>
       <c r="E18" s="3">
-        <v>50300</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
+        <v>54900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>49000</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
@@ -1000,9 +1029,12 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,19 +1047,20 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>15100</v>
       </c>
       <c r="E20" s="3">
-        <v>14400</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
+        <v>49500</v>
+      </c>
+      <c r="F20" s="3">
+        <v>14000</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1044,20 +1077,23 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>75800</v>
+        <v>91100</v>
       </c>
       <c r="E21" s="3">
-        <v>74600</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
+        <v>123400</v>
+      </c>
+      <c r="F21" s="3">
+        <v>72700</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1074,20 +1110,23 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>15200</v>
+        <v>30300</v>
       </c>
       <c r="E22" s="3">
-        <v>21400</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+        <v>64200</v>
+      </c>
+      <c r="F22" s="3">
+        <v>20900</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1104,20 +1143,23 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>41200</v>
+        <v>41900</v>
       </c>
       <c r="E23" s="3">
-        <v>43300</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
+        <v>40100</v>
+      </c>
+      <c r="F23" s="3">
+        <v>42200</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>3</v>
@@ -1134,20 +1176,23 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>15300</v>
+        <v>15400</v>
       </c>
       <c r="E24" s="3">
-        <v>17400</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+        <v>21000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>16900</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1164,9 +1209,12 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,20 +1242,23 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>25900</v>
+        <v>26600</v>
       </c>
       <c r="E26" s="3">
-        <v>25900</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
+        <v>19200</v>
+      </c>
+      <c r="F26" s="3">
+        <v>25200</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>3</v>
@@ -1224,20 +1275,23 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>25900</v>
+        <v>26600</v>
       </c>
       <c r="E27" s="3">
-        <v>25900</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
+        <v>19200</v>
+      </c>
+      <c r="F27" s="3">
+        <v>25200</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1254,9 +1308,12 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1314,9 +1374,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,20 +1440,23 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-15100</v>
       </c>
       <c r="E32" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
+        <v>-49500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-14000</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1404,20 +1473,23 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>25900</v>
+        <v>26600</v>
       </c>
       <c r="E33" s="3">
-        <v>25900</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
+        <v>19200</v>
+      </c>
+      <c r="F33" s="3">
+        <v>25200</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1434,9 +1506,12 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,20 +1539,23 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>25900</v>
+        <v>26600</v>
       </c>
       <c r="E35" s="3">
-        <v>25900</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
+        <v>19200</v>
+      </c>
+      <c r="F35" s="3">
+        <v>25200</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -1494,26 +1572,29 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="G38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1529,9 +1610,12 @@
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,19 +1643,20 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>26200</v>
+        <v>42400</v>
       </c>
       <c r="E41" s="3">
-        <v>27900</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
+        <v>62700</v>
+      </c>
+      <c r="F41" s="3">
+        <v>27200</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -1587,20 +1673,23 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>31800</v>
+        <v>600</v>
       </c>
       <c r="E42" s="3">
-        <v>164300</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
+        <v>31000</v>
+      </c>
+      <c r="F42" s="3">
+        <v>160100</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
@@ -1617,20 +1706,23 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>150000</v>
+        <v>132400</v>
       </c>
       <c r="E43" s="3">
-        <v>99800</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
+        <v>248800</v>
+      </c>
+      <c r="F43" s="3">
+        <v>97300</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
@@ -1647,9 +1739,12 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1677,20 +1772,23 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>14200</v>
+        <v>7400</v>
       </c>
       <c r="E45" s="3">
-        <v>6400</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
+        <v>13800</v>
+      </c>
+      <c r="F45" s="3">
+        <v>6200</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -1707,20 +1805,23 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>222200</v>
+        <v>182800</v>
       </c>
       <c r="E46" s="3">
-        <v>298300</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
+        <v>214700</v>
+      </c>
+      <c r="F46" s="3">
+        <v>290800</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
@@ -1737,21 +1838,24 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>200</v>
+      </c>
+      <c r="E47" s="3">
         <v>700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>600</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1767,20 +1871,23 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>22900</v>
+        <v>15700</v>
       </c>
       <c r="E48" s="3">
-        <v>27100</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
+        <v>33400</v>
+      </c>
+      <c r="F48" s="3">
+        <v>26400</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1797,20 +1904,23 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>360000</v>
+        <v>334700</v>
       </c>
       <c r="E49" s="3">
-        <v>151900</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
+        <v>702900</v>
+      </c>
+      <c r="F49" s="3">
+        <v>148100</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
@@ -1827,9 +1937,12 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,20 +2003,23 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>16500</v>
+        <v>11200</v>
       </c>
       <c r="E52" s="3">
-        <v>7800</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+        <v>18500</v>
+      </c>
+      <c r="F52" s="3">
+        <v>7600</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
@@ -1917,9 +2036,12 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,20 +2069,23 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>622400</v>
+        <v>544500</v>
       </c>
       <c r="E54" s="3">
-        <v>485800</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
+        <v>601900</v>
+      </c>
+      <c r="F54" s="3">
+        <v>473500</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -1977,9 +2102,12 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,19 +2135,20 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>21600</v>
+        <v>7000</v>
       </c>
       <c r="E57" s="3">
-        <v>17000</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
+        <v>22100</v>
+      </c>
+      <c r="F57" s="3">
+        <v>16500</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2035,20 +2165,23 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>47600</v>
+        <v>22600</v>
       </c>
       <c r="E58" s="3">
-        <v>33800</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+        <v>47300</v>
+      </c>
+      <c r="F58" s="3">
+        <v>32900</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -2065,20 +2198,23 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>86100</v>
+        <v>61600</v>
       </c>
       <c r="E59" s="3">
-        <v>62100</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
+        <v>77700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>60500</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2095,20 +2231,23 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>155300</v>
+        <v>91200</v>
       </c>
       <c r="E60" s="3">
-        <v>112900</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
+        <v>146300</v>
+      </c>
+      <c r="F60" s="3">
+        <v>110000</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
@@ -2125,20 +2264,23 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>152800</v>
+        <v>123200</v>
       </c>
       <c r="E61" s="3">
-        <v>128400</v>
+        <v>151100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>125100</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2155,20 +2297,23 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>39200</v>
+        <v>47200</v>
       </c>
       <c r="E62" s="3">
-        <v>20500</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
+        <v>43100</v>
+      </c>
+      <c r="F62" s="3">
+        <v>20000</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -2185,9 +2330,12 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,20 +2429,23 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>347200</v>
+        <v>261700</v>
       </c>
       <c r="E66" s="3">
-        <v>261800</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
+        <v>339700</v>
+      </c>
+      <c r="F66" s="3">
+        <v>255100</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -2305,9 +2462,12 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,20 +2609,23 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>93600</v>
+        <v>105900</v>
       </c>
       <c r="E72" s="3">
-        <v>28000</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
+        <v>85200</v>
+      </c>
+      <c r="F72" s="3">
+        <v>27300</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -2469,9 +2642,12 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,20 +2741,23 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>275200</v>
+        <v>282800</v>
       </c>
       <c r="E76" s="3">
-        <v>224000</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
+        <v>262100</v>
+      </c>
+      <c r="F76" s="3">
+        <v>218300</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
@@ -2589,9 +2774,12 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,26 +2807,29 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="G80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2654,20 +2845,23 @@
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>25900</v>
+        <v>26600</v>
       </c>
       <c r="E81" s="3">
-        <v>25900</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
+        <v>19200</v>
+      </c>
+      <c r="F81" s="3">
+        <v>25200</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
@@ -2684,9 +2878,12 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,19 +2896,20 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>19400</v>
+        <v>18700</v>
       </c>
       <c r="E83" s="3">
-        <v>9900</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
+        <v>19000</v>
+      </c>
+      <c r="F83" s="3">
+        <v>9700</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -2728,9 +2926,12 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,20 +3091,23 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>7400</v>
+        <v>59200</v>
       </c>
       <c r="E89" s="3">
-        <v>27200</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
+        <v>7200</v>
+      </c>
+      <c r="F89" s="3">
+        <v>26500</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
@@ -2908,9 +3124,12 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,8 +3142,9 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2952,9 +3172,12 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,20 +3238,23 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-17000</v>
+        <v>13300</v>
       </c>
       <c r="E94" s="3">
-        <v>-310000</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
+        <v>-16500</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-302100</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -3042,9 +3271,12 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,8 +3289,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3066,10 +3299,10 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-25900</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-25300</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -3086,9 +3319,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,20 +3418,23 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>20700</v>
+        <v>-66800</v>
       </c>
       <c r="E100" s="3">
-        <v>283100</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
+        <v>20200</v>
+      </c>
+      <c r="F100" s="3">
+        <v>275900</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -3206,17 +3451,20 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-800</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3233,24 +3481,27 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>10300</v>
+        <v>5200</v>
       </c>
       <c r="E102" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3266,7 +3517,10 @@
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -715,13 +715,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>447600</v>
+        <v>412700</v>
       </c>
       <c r="E8" s="3">
-        <v>438500</v>
+        <v>404200</v>
       </c>
       <c r="F8" s="3">
-        <v>289500</v>
+        <v>266900</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -748,13 +748,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>298200</v>
+        <v>274900</v>
       </c>
       <c r="E9" s="3">
-        <v>571300</v>
+        <v>263300</v>
       </c>
       <c r="F9" s="3">
-        <v>187500</v>
+        <v>172900</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -781,13 +781,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>149500</v>
+        <v>137800</v>
       </c>
       <c r="E10" s="3">
-        <v>-132800</v>
+        <v>140900</v>
       </c>
       <c r="F10" s="3">
-        <v>101900</v>
+        <v>94000</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -895,10 +895,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="E14" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="F14" s="3">
         <v>100</v>
@@ -973,13 +973,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>390400</v>
+        <v>359900</v>
       </c>
       <c r="E17" s="3">
-        <v>383600</v>
+        <v>353600</v>
       </c>
       <c r="F17" s="3">
-        <v>240500</v>
+        <v>221700</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>3</v>
@@ -1006,13 +1006,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>57200</v>
+        <v>52700</v>
       </c>
       <c r="E18" s="3">
-        <v>54900</v>
+        <v>50600</v>
       </c>
       <c r="F18" s="3">
-        <v>49000</v>
+        <v>45200</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
@@ -1054,13 +1054,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>15100</v>
+        <v>1400</v>
       </c>
       <c r="E20" s="3">
-        <v>49500</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>14000</v>
+        <v>12900</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1087,13 +1087,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>91100</v>
+        <v>71500</v>
       </c>
       <c r="E21" s="3">
-        <v>123400</v>
+        <v>68300</v>
       </c>
       <c r="F21" s="3">
-        <v>72700</v>
+        <v>67100</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1120,13 +1120,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>30300</v>
+        <v>15400</v>
       </c>
       <c r="E22" s="3">
-        <v>64200</v>
+        <v>13600</v>
       </c>
       <c r="F22" s="3">
-        <v>20900</v>
+        <v>19200</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1153,13 +1153,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>41900</v>
+        <v>38700</v>
       </c>
       <c r="E23" s="3">
-        <v>40100</v>
+        <v>37000</v>
       </c>
       <c r="F23" s="3">
-        <v>42200</v>
+        <v>38900</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>3</v>
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>15400</v>
+        <v>14200</v>
       </c>
       <c r="E24" s="3">
-        <v>21000</v>
+        <v>19300</v>
       </c>
       <c r="F24" s="3">
-        <v>16900</v>
+        <v>15600</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1252,13 +1252,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>26600</v>
+        <v>24500</v>
       </c>
       <c r="E26" s="3">
-        <v>19200</v>
+        <v>17700</v>
       </c>
       <c r="F26" s="3">
-        <v>25200</v>
+        <v>23300</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>3</v>
@@ -1285,13 +1285,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>26600</v>
+        <v>24500</v>
       </c>
       <c r="E27" s="3">
-        <v>19200</v>
+        <v>17700</v>
       </c>
       <c r="F27" s="3">
-        <v>25200</v>
+        <v>23300</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1450,13 +1450,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-15100</v>
+        <v>-1400</v>
       </c>
       <c r="E32" s="3">
-        <v>-49500</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-14000</v>
+        <v>-12900</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1483,13 +1483,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>26600</v>
+        <v>24500</v>
       </c>
       <c r="E33" s="3">
-        <v>19200</v>
+        <v>17700</v>
       </c>
       <c r="F33" s="3">
-        <v>25200</v>
+        <v>23300</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1549,13 +1549,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>26600</v>
+        <v>24500</v>
       </c>
       <c r="E35" s="3">
-        <v>19200</v>
+        <v>17700</v>
       </c>
       <c r="F35" s="3">
-        <v>25200</v>
+        <v>23300</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -1650,13 +1650,13 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>42400</v>
+        <v>11800</v>
       </c>
       <c r="E41" s="3">
-        <v>62700</v>
+        <v>23500</v>
       </c>
       <c r="F41" s="3">
-        <v>27200</v>
+        <v>25100</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -1683,13 +1683,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>600</v>
+        <v>27900</v>
       </c>
       <c r="E42" s="3">
-        <v>31000</v>
+        <v>28600</v>
       </c>
       <c r="F42" s="3">
-        <v>160100</v>
+        <v>147600</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
@@ -1716,13 +1716,13 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>132400</v>
+        <v>122100</v>
       </c>
       <c r="E43" s="3">
-        <v>248800</v>
+        <v>136700</v>
       </c>
       <c r="F43" s="3">
-        <v>97300</v>
+        <v>89700</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
@@ -1782,13 +1782,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7400</v>
+        <v>6800</v>
       </c>
       <c r="E45" s="3">
-        <v>13800</v>
+        <v>12800</v>
       </c>
       <c r="F45" s="3">
-        <v>6200</v>
+        <v>5700</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -1815,13 +1815,13 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>182800</v>
+        <v>168500</v>
       </c>
       <c r="E46" s="3">
-        <v>214700</v>
+        <v>197900</v>
       </c>
       <c r="F46" s="3">
-        <v>290800</v>
+        <v>268100</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
@@ -1881,13 +1881,13 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>15700</v>
+        <v>14500</v>
       </c>
       <c r="E48" s="3">
-        <v>33400</v>
+        <v>20600</v>
       </c>
       <c r="F48" s="3">
-        <v>26400</v>
+        <v>24300</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1914,13 +1914,13 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>334700</v>
+        <v>308500</v>
       </c>
       <c r="E49" s="3">
-        <v>702900</v>
+        <v>324400</v>
       </c>
       <c r="F49" s="3">
-        <v>148100</v>
+        <v>136500</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
@@ -2013,13 +2013,13 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E52" s="3">
         <v>11200</v>
       </c>
-      <c r="E52" s="3">
-        <v>18500</v>
-      </c>
       <c r="F52" s="3">
-        <v>7600</v>
+        <v>7000</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
@@ -2079,13 +2079,13 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>544500</v>
+        <v>502000</v>
       </c>
       <c r="E54" s="3">
-        <v>601900</v>
+        <v>554800</v>
       </c>
       <c r="F54" s="3">
-        <v>473500</v>
+        <v>436500</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -2142,13 +2142,13 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>7000</v>
+        <v>6500</v>
       </c>
       <c r="E57" s="3">
-        <v>22100</v>
+        <v>20300</v>
       </c>
       <c r="F57" s="3">
-        <v>16500</v>
+        <v>15200</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2175,13 +2175,13 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>22600</v>
+        <v>20800</v>
       </c>
       <c r="E58" s="3">
-        <v>47300</v>
+        <v>43600</v>
       </c>
       <c r="F58" s="3">
-        <v>32900</v>
+        <v>30400</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -2208,13 +2208,13 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>61600</v>
+        <v>56800</v>
       </c>
       <c r="E59" s="3">
-        <v>77700</v>
+        <v>77400</v>
       </c>
       <c r="F59" s="3">
-        <v>60500</v>
+        <v>55800</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2241,13 +2241,13 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>91200</v>
+        <v>84100</v>
       </c>
       <c r="E60" s="3">
-        <v>146300</v>
+        <v>134800</v>
       </c>
       <c r="F60" s="3">
-        <v>110000</v>
+        <v>101400</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
@@ -2274,13 +2274,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>123200</v>
+        <v>113600</v>
       </c>
       <c r="E61" s="3">
-        <v>151100</v>
+        <v>139300</v>
       </c>
       <c r="F61" s="3">
-        <v>125100</v>
+        <v>115300</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2307,13 +2307,13 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>47200</v>
+        <v>43500</v>
       </c>
       <c r="E62" s="3">
-        <v>43100</v>
+        <v>39100</v>
       </c>
       <c r="F62" s="3">
-        <v>20000</v>
+        <v>18400</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -2439,13 +2439,13 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>261700</v>
+        <v>241200</v>
       </c>
       <c r="E66" s="3">
-        <v>339700</v>
+        <v>313200</v>
       </c>
       <c r="F66" s="3">
-        <v>255100</v>
+        <v>235200</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -2619,13 +2619,13 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>105900</v>
+        <v>97600</v>
       </c>
       <c r="E72" s="3">
-        <v>85200</v>
+        <v>78500</v>
       </c>
       <c r="F72" s="3">
-        <v>27300</v>
+        <v>25100</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -2751,13 +2751,13 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>282800</v>
+        <v>260700</v>
       </c>
       <c r="E76" s="3">
-        <v>262100</v>
+        <v>241700</v>
       </c>
       <c r="F76" s="3">
-        <v>218300</v>
+        <v>201300</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
@@ -2855,13 +2855,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>26600</v>
+        <v>24500</v>
       </c>
       <c r="E81" s="3">
-        <v>19200</v>
+        <v>17700</v>
       </c>
       <c r="F81" s="3">
-        <v>25200</v>
+        <v>23300</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
@@ -2903,13 +2903,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>18700</v>
+        <v>17200</v>
       </c>
       <c r="E83" s="3">
-        <v>19000</v>
+        <v>17500</v>
       </c>
       <c r="F83" s="3">
-        <v>9700</v>
+        <v>8900</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -3101,13 +3101,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>59200</v>
+        <v>54500</v>
       </c>
       <c r="E89" s="3">
-        <v>7200</v>
+        <v>6700</v>
       </c>
       <c r="F89" s="3">
-        <v>26500</v>
+        <v>24200</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
@@ -3248,13 +3248,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>13300</v>
+        <v>12200</v>
       </c>
       <c r="E94" s="3">
-        <v>-16500</v>
+        <v>-15300</v>
       </c>
       <c r="F94" s="3">
-        <v>-302100</v>
+        <v>-278300</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-25300</v>
+        <v>-23300</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-66800</v>
+        <v>-61600</v>
       </c>
       <c r="E100" s="3">
-        <v>20200</v>
+        <v>18600</v>
       </c>
       <c r="F100" s="3">
-        <v>275900</v>
+        <v>254400</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -3466,8 +3466,8 @@
       <c r="E101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
+      <c r="F101" s="3">
+        <v>-5300</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
@@ -3494,13 +3494,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>5200</v>
+        <v>4800</v>
       </c>
       <c r="E102" s="3">
-        <v>10000</v>
+        <v>9200</v>
       </c>
       <c r="F102" s="3">
-        <v>300</v>
+        <v>-5000</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
@@ -715,13 +715,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>412700</v>
+        <v>401400</v>
       </c>
       <c r="E8" s="3">
-        <v>404200</v>
+        <v>393200</v>
       </c>
       <c r="F8" s="3">
-        <v>266900</v>
+        <v>259600</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -748,13 +748,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>274900</v>
+        <v>267400</v>
       </c>
       <c r="E9" s="3">
-        <v>263300</v>
+        <v>256200</v>
       </c>
       <c r="F9" s="3">
-        <v>172900</v>
+        <v>168200</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -781,13 +781,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>137800</v>
+        <v>134000</v>
       </c>
       <c r="E10" s="3">
-        <v>140900</v>
+        <v>137000</v>
       </c>
       <c r="F10" s="3">
-        <v>94000</v>
+        <v>91400</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -898,7 +898,7 @@
         <v>1200</v>
       </c>
       <c r="E14" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="F14" s="3">
         <v>100</v>
@@ -973,13 +973,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>359900</v>
+        <v>350100</v>
       </c>
       <c r="E17" s="3">
-        <v>353600</v>
+        <v>344000</v>
       </c>
       <c r="F17" s="3">
-        <v>221700</v>
+        <v>215600</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>3</v>
@@ -1006,13 +1006,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>52700</v>
+        <v>51300</v>
       </c>
       <c r="E18" s="3">
-        <v>50600</v>
+        <v>49200</v>
       </c>
       <c r="F18" s="3">
-        <v>45200</v>
+        <v>44000</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
@@ -1054,13 +1054,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>12900</v>
+        <v>12500</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1087,13 +1087,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>71500</v>
+        <v>69200</v>
       </c>
       <c r="E21" s="3">
-        <v>68300</v>
+        <v>66100</v>
       </c>
       <c r="F21" s="3">
-        <v>67100</v>
+        <v>65100</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1120,13 +1120,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="E22" s="3">
-        <v>13600</v>
+        <v>13300</v>
       </c>
       <c r="F22" s="3">
-        <v>19200</v>
+        <v>18700</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1153,13 +1153,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>38700</v>
+        <v>37600</v>
       </c>
       <c r="E23" s="3">
-        <v>37000</v>
+        <v>36000</v>
       </c>
       <c r="F23" s="3">
-        <v>38900</v>
+        <v>37800</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>3</v>
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>14200</v>
+        <v>13800</v>
       </c>
       <c r="E24" s="3">
-        <v>19300</v>
+        <v>18800</v>
       </c>
       <c r="F24" s="3">
-        <v>15600</v>
+        <v>15200</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1252,13 +1252,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>24500</v>
+        <v>23800</v>
       </c>
       <c r="E26" s="3">
-        <v>17700</v>
+        <v>17200</v>
       </c>
       <c r="F26" s="3">
-        <v>23300</v>
+        <v>22600</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>3</v>
@@ -1285,13 +1285,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>24500</v>
+        <v>23800</v>
       </c>
       <c r="E27" s="3">
-        <v>17700</v>
+        <v>17200</v>
       </c>
       <c r="F27" s="3">
-        <v>23300</v>
+        <v>22600</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1450,13 +1450,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1400</v>
+        <v>-1300</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-12900</v>
+        <v>-12500</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1483,13 +1483,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>24500</v>
+        <v>23800</v>
       </c>
       <c r="E33" s="3">
-        <v>17700</v>
+        <v>17200</v>
       </c>
       <c r="F33" s="3">
-        <v>23300</v>
+        <v>22600</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1549,13 +1549,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>24500</v>
+        <v>23800</v>
       </c>
       <c r="E35" s="3">
-        <v>17700</v>
+        <v>17200</v>
       </c>
       <c r="F35" s="3">
-        <v>23300</v>
+        <v>22600</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -1650,13 +1650,13 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>11800</v>
+        <v>11400</v>
       </c>
       <c r="E41" s="3">
-        <v>23500</v>
+        <v>22900</v>
       </c>
       <c r="F41" s="3">
-        <v>25100</v>
+        <v>24400</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -1683,13 +1683,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>27900</v>
+        <v>27200</v>
       </c>
       <c r="E42" s="3">
-        <v>28600</v>
+        <v>27800</v>
       </c>
       <c r="F42" s="3">
-        <v>147600</v>
+        <v>143600</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
@@ -1716,13 +1716,13 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>122100</v>
+        <v>118700</v>
       </c>
       <c r="E43" s="3">
-        <v>136700</v>
+        <v>133000</v>
       </c>
       <c r="F43" s="3">
-        <v>89700</v>
+        <v>87300</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
@@ -1782,13 +1782,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="E45" s="3">
-        <v>12800</v>
+        <v>12400</v>
       </c>
       <c r="F45" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -1815,13 +1815,13 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>168500</v>
+        <v>163900</v>
       </c>
       <c r="E46" s="3">
-        <v>197900</v>
+        <v>192500</v>
       </c>
       <c r="F46" s="3">
-        <v>268100</v>
+        <v>260800</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
@@ -1854,7 +1854,7 @@
         <v>700</v>
       </c>
       <c r="F47" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -1881,13 +1881,13 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>14500</v>
+        <v>14100</v>
       </c>
       <c r="E48" s="3">
-        <v>20600</v>
+        <v>20000</v>
       </c>
       <c r="F48" s="3">
-        <v>24300</v>
+        <v>23600</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1914,13 +1914,13 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>308500</v>
+        <v>300100</v>
       </c>
       <c r="E49" s="3">
-        <v>324400</v>
+        <v>315600</v>
       </c>
       <c r="F49" s="3">
-        <v>136500</v>
+        <v>132800</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
@@ -2013,13 +2013,13 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10300</v>
+        <v>10000</v>
       </c>
       <c r="E52" s="3">
-        <v>11200</v>
+        <v>10900</v>
       </c>
       <c r="F52" s="3">
-        <v>7000</v>
+        <v>6800</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
@@ -2079,13 +2079,13 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>502000</v>
+        <v>488300</v>
       </c>
       <c r="E54" s="3">
-        <v>554800</v>
+        <v>539700</v>
       </c>
       <c r="F54" s="3">
-        <v>436500</v>
+        <v>424600</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -2142,13 +2142,13 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6500</v>
+        <v>6300</v>
       </c>
       <c r="E57" s="3">
-        <v>20300</v>
+        <v>19800</v>
       </c>
       <c r="F57" s="3">
-        <v>15200</v>
+        <v>14800</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2175,13 +2175,13 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>20800</v>
+        <v>23500</v>
       </c>
       <c r="E58" s="3">
-        <v>43600</v>
+        <v>46300</v>
       </c>
       <c r="F58" s="3">
-        <v>30400</v>
+        <v>33400</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -2208,13 +2208,13 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>56800</v>
+        <v>52100</v>
       </c>
       <c r="E59" s="3">
-        <v>77400</v>
+        <v>71400</v>
       </c>
       <c r="F59" s="3">
-        <v>55800</v>
+        <v>50500</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2241,13 +2241,13 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>84100</v>
+        <v>81800</v>
       </c>
       <c r="E60" s="3">
-        <v>134800</v>
+        <v>131200</v>
       </c>
       <c r="F60" s="3">
-        <v>101400</v>
+        <v>98700</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
@@ -2274,13 +2274,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>113600</v>
+        <v>115300</v>
       </c>
       <c r="E61" s="3">
-        <v>139300</v>
+        <v>142900</v>
       </c>
       <c r="F61" s="3">
-        <v>115300</v>
+        <v>123100</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2307,13 +2307,13 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>43500</v>
+        <v>37500</v>
       </c>
       <c r="E62" s="3">
-        <v>39100</v>
+        <v>30600</v>
       </c>
       <c r="F62" s="3">
-        <v>18400</v>
+        <v>7000</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -2439,13 +2439,13 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>241200</v>
+        <v>234700</v>
       </c>
       <c r="E66" s="3">
-        <v>313200</v>
+        <v>304600</v>
       </c>
       <c r="F66" s="3">
-        <v>235200</v>
+        <v>228800</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -2619,13 +2619,13 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>97600</v>
+        <v>95000</v>
       </c>
       <c r="E72" s="3">
-        <v>78500</v>
+        <v>76400</v>
       </c>
       <c r="F72" s="3">
-        <v>25100</v>
+        <v>24500</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -2751,13 +2751,13 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>260700</v>
+        <v>253600</v>
       </c>
       <c r="E76" s="3">
-        <v>241700</v>
+        <v>235100</v>
       </c>
       <c r="F76" s="3">
-        <v>201300</v>
+        <v>195800</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
@@ -2855,13 +2855,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>24500</v>
+        <v>23800</v>
       </c>
       <c r="E81" s="3">
-        <v>17700</v>
+        <v>17200</v>
       </c>
       <c r="F81" s="3">
-        <v>23300</v>
+        <v>22600</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
@@ -2903,13 +2903,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>17200</v>
+        <v>16800</v>
       </c>
       <c r="E83" s="3">
-        <v>17500</v>
+        <v>17000</v>
       </c>
       <c r="F83" s="3">
-        <v>8900</v>
+        <v>8700</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -3101,13 +3101,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>54500</v>
+        <v>53100</v>
       </c>
       <c r="E89" s="3">
-        <v>6700</v>
+        <v>6500</v>
       </c>
       <c r="F89" s="3">
-        <v>24200</v>
+        <v>23600</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
@@ -3248,13 +3248,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>12200</v>
+        <v>11900</v>
       </c>
       <c r="E94" s="3">
-        <v>-15300</v>
+        <v>-14800</v>
       </c>
       <c r="F94" s="3">
-        <v>-278300</v>
+        <v>-270700</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-23300</v>
+        <v>-22700</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-61600</v>
+        <v>-59900</v>
       </c>
       <c r="E100" s="3">
-        <v>18600</v>
+        <v>18100</v>
       </c>
       <c r="F100" s="3">
-        <v>254400</v>
+        <v>247400</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -3467,7 +3467,7 @@
         <v>-800</v>
       </c>
       <c r="F101" s="3">
-        <v>-5300</v>
+        <v>-5200</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
@@ -3494,13 +3494,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="E102" s="3">
-        <v>9200</v>
+        <v>9000</v>
       </c>
       <c r="F102" s="3">
-        <v>-5000</v>
+        <v>-4900</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -690,17 +690,17 @@
       <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="G7" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H7" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I7" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J7" s="2">
+        <v>43100</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -715,25 +715,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>401400</v>
+        <v>460300</v>
       </c>
       <c r="E8" s="3">
-        <v>393200</v>
+        <v>413800</v>
       </c>
       <c r="F8" s="3">
-        <v>259600</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>259200</v>
+      </c>
+      <c r="G8" s="3">
+        <v>184200</v>
+      </c>
+      <c r="H8" s="3">
+        <v>168500</v>
+      </c>
+      <c r="I8" s="3">
+        <v>152000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>136600</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -748,25 +748,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>267400</v>
+        <v>306600</v>
       </c>
       <c r="E9" s="3">
-        <v>256200</v>
+        <v>269600</v>
       </c>
       <c r="F9" s="3">
-        <v>168200</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>167900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>115700</v>
+      </c>
+      <c r="H9" s="3">
+        <v>111700</v>
+      </c>
+      <c r="I9" s="3">
+        <v>97700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>94900</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -781,25 +781,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>134000</v>
+        <v>153700</v>
       </c>
       <c r="E10" s="3">
-        <v>137000</v>
+        <v>144200</v>
       </c>
       <c r="F10" s="3">
-        <v>91400</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>91300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>68500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>56800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>54300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>41700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -828,26 +828,26 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>400</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="G12" s="3">
+        <v>700</v>
+      </c>
+      <c r="H12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J12" s="3">
+        <v>4600</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -894,14 +894,14 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>1200</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2100</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>100</v>
+        <v>3900</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -928,19 +928,19 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>13700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>12200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -973,25 +973,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>350100</v>
+        <v>401500</v>
       </c>
       <c r="E17" s="3">
-        <v>344000</v>
+        <v>362000</v>
       </c>
       <c r="F17" s="3">
-        <v>215600</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>211400</v>
+      </c>
+      <c r="G17" s="3">
+        <v>144100</v>
+      </c>
+      <c r="H17" s="3">
+        <v>145600</v>
+      </c>
+      <c r="I17" s="3">
+        <v>128000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>123300</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1006,25 +1006,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>51300</v>
+        <v>58800</v>
       </c>
       <c r="E18" s="3">
-        <v>49200</v>
+        <v>51800</v>
       </c>
       <c r="F18" s="3">
-        <v>44000</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>47800</v>
+      </c>
+      <c r="G18" s="3">
+        <v>40100</v>
+      </c>
+      <c r="H18" s="3">
+        <v>22800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>24000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>13200</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1054,19 +1054,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F20" s="3">
-        <v>12500</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+        <v>1600</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H20" s="3">
+        <v>100</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1087,25 +1087,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>69200</v>
+        <v>72000</v>
       </c>
       <c r="E21" s="3">
-        <v>66100</v>
+        <v>62100</v>
       </c>
       <c r="F21" s="3">
-        <v>65100</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>54900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>44300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>24800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>24000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>13200</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1120,25 +1120,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>15000</v>
+        <v>17200</v>
       </c>
       <c r="E22" s="3">
-        <v>13300</v>
+        <v>14000</v>
       </c>
       <c r="F22" s="3">
-        <v>18700</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>5300</v>
+      </c>
+      <c r="G22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J22" s="3">
+        <v>100</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1153,25 +1153,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>37600</v>
+        <v>43100</v>
       </c>
       <c r="E23" s="3">
-        <v>36000</v>
+        <v>37900</v>
       </c>
       <c r="F23" s="3">
         <v>37800</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+      <c r="G23" s="3">
+        <v>37100</v>
+      </c>
+      <c r="H23" s="3">
+        <v>21300</v>
+      </c>
+      <c r="I23" s="3">
+        <v>22500</v>
+      </c>
+      <c r="J23" s="3">
+        <v>13100</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1186,25 +1186,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>13800</v>
+        <v>15800</v>
       </c>
       <c r="E24" s="3">
-        <v>18800</v>
+        <v>19800</v>
       </c>
       <c r="F24" s="3">
         <v>15200</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>12500</v>
+      </c>
+      <c r="H24" s="3">
+        <v>7300</v>
+      </c>
+      <c r="I24" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J24" s="3">
+        <v>4300</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1252,25 +1252,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>23800</v>
+        <v>27300</v>
       </c>
       <c r="E26" s="3">
-        <v>17200</v>
+        <v>18100</v>
       </c>
       <c r="F26" s="3">
         <v>22600</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+      <c r="G26" s="3">
+        <v>24600</v>
+      </c>
+      <c r="H26" s="3">
+        <v>14100</v>
+      </c>
+      <c r="I26" s="3">
+        <v>15800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>8800</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1285,25 +1285,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>23800</v>
+        <v>27300</v>
       </c>
       <c r="E27" s="3">
-        <v>17200</v>
+        <v>18100</v>
       </c>
       <c r="F27" s="3">
         <v>22600</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+      <c r="G27" s="3">
+        <v>24600</v>
+      </c>
+      <c r="H27" s="3">
+        <v>14100</v>
+      </c>
+      <c r="I27" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>8700</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1450,19 +1450,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1300</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="F32" s="3">
-        <v>-12500</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+        <v>-1600</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-100</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1483,25 +1483,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>23800</v>
+        <v>27300</v>
       </c>
       <c r="E33" s="3">
-        <v>17200</v>
+        <v>18100</v>
       </c>
       <c r="F33" s="3">
         <v>22600</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+      <c r="G33" s="3">
+        <v>24600</v>
+      </c>
+      <c r="H33" s="3">
+        <v>14100</v>
+      </c>
+      <c r="I33" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>8700</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1549,25 +1549,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>23800</v>
+        <v>27300</v>
       </c>
       <c r="E35" s="3">
-        <v>17200</v>
+        <v>18100</v>
       </c>
       <c r="F35" s="3">
         <v>22600</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+      <c r="G35" s="3">
+        <v>24600</v>
+      </c>
+      <c r="H35" s="3">
+        <v>14100</v>
+      </c>
+      <c r="I35" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>8700</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1595,17 +1595,17 @@
       <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="G38" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H38" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I38" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J38" s="2">
+        <v>43100</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1650,25 +1650,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>11400</v>
+        <v>43600</v>
       </c>
       <c r="E41" s="3">
-        <v>22900</v>
+        <v>35100</v>
       </c>
       <c r="F41" s="3">
         <v>24400</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="G41" s="3">
+        <v>31400</v>
+      </c>
+      <c r="H41" s="3">
+        <v>19800</v>
+      </c>
+      <c r="I41" s="3">
+        <v>19900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>12400</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1683,25 +1683,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>27200</v>
+        <v>700</v>
       </c>
       <c r="E42" s="3">
-        <v>27800</v>
+        <v>18200</v>
       </c>
       <c r="F42" s="3">
-        <v>143600</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>143400</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1716,25 +1716,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>118700</v>
+        <v>136200</v>
       </c>
       <c r="E43" s="3">
-        <v>133000</v>
+        <v>139900</v>
       </c>
       <c r="F43" s="3">
-        <v>87300</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>87100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>48100</v>
+      </c>
+      <c r="H43" s="3">
+        <v>41600</v>
+      </c>
+      <c r="I43" s="3">
+        <v>39600</v>
+      </c>
+      <c r="J43" s="3">
+        <v>35900</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1748,26 +1748,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1782,25 +1782,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6600</v>
+        <v>7600</v>
       </c>
       <c r="E45" s="3">
-        <v>12400</v>
+        <v>9400</v>
       </c>
       <c r="F45" s="3">
-        <v>5600</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>5500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I45" s="3">
+        <v>300</v>
+      </c>
+      <c r="J45" s="3">
+        <v>100</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1815,25 +1815,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>163900</v>
+        <v>188000</v>
       </c>
       <c r="E46" s="3">
-        <v>192500</v>
+        <v>202600</v>
       </c>
       <c r="F46" s="3">
-        <v>260800</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>260400</v>
+      </c>
+      <c r="G46" s="3">
+        <v>83700</v>
+      </c>
+      <c r="H46" s="3">
+        <v>63500</v>
+      </c>
+      <c r="I46" s="3">
+        <v>59800</v>
+      </c>
+      <c r="J46" s="3">
+        <v>48400</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1847,14 +1847,14 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>200</v>
-      </c>
-      <c r="E47" s="3">
-        <v>700</v>
-      </c>
-      <c r="F47" s="3">
-        <v>500</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -1862,11 +1862,11 @@
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+      <c r="I47" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1600</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1881,25 +1881,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>14100</v>
+        <v>16100</v>
       </c>
       <c r="E48" s="3">
-        <v>20000</v>
+        <v>21100</v>
       </c>
       <c r="F48" s="3">
         <v>23600</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="G48" s="3">
+        <v>20900</v>
+      </c>
+      <c r="H48" s="3">
+        <v>25300</v>
+      </c>
+      <c r="I48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J48" s="3">
+        <v>6000</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1914,25 +1914,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>300100</v>
+        <v>344100</v>
       </c>
       <c r="E49" s="3">
-        <v>315600</v>
+        <v>332200</v>
       </c>
       <c r="F49" s="3">
-        <v>132800</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>132600</v>
+      </c>
+      <c r="G49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H49" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I49" s="3">
+        <v>6300</v>
+      </c>
+      <c r="J49" s="3">
+        <v>8000</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2013,25 +2013,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10000</v>
+        <v>7900</v>
       </c>
       <c r="E52" s="3">
-        <v>10900</v>
+        <v>9200</v>
       </c>
       <c r="F52" s="3">
-        <v>6800</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>1600</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I52" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J52" s="3">
+        <v>2100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2079,25 +2079,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>488300</v>
+        <v>559900</v>
       </c>
       <c r="E54" s="3">
-        <v>539700</v>
+        <v>568000</v>
       </c>
       <c r="F54" s="3">
-        <v>424600</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>424000</v>
+      </c>
+      <c r="G54" s="3">
+        <v>112700</v>
+      </c>
+      <c r="H54" s="3">
+        <v>101400</v>
+      </c>
+      <c r="I54" s="3">
+        <v>76500</v>
+      </c>
+      <c r="J54" s="3">
+        <v>67400</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2142,25 +2142,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E57" s="3">
         <v>6300</v>
       </c>
-      <c r="E57" s="3">
-        <v>19800</v>
-      </c>
       <c r="F57" s="3">
-        <v>14800</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>6000</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1400</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2175,25 +2175,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>23500</v>
+        <v>26900</v>
       </c>
       <c r="E58" s="3">
-        <v>46300</v>
+        <v>48700</v>
       </c>
       <c r="F58" s="3">
-        <v>33400</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>33300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>17300</v>
+      </c>
+      <c r="H58" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>4900</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2208,25 +2208,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>52100</v>
+        <v>18800</v>
       </c>
       <c r="E59" s="3">
-        <v>71400</v>
+        <v>31100</v>
       </c>
       <c r="F59" s="3">
-        <v>50500</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>16200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>11700</v>
+      </c>
+      <c r="H59" s="3">
+        <v>22800</v>
+      </c>
+      <c r="I59" s="3">
+        <v>11000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>9500</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2241,25 +2241,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>81800</v>
+        <v>93800</v>
       </c>
       <c r="E60" s="3">
-        <v>131200</v>
+        <v>138100</v>
       </c>
       <c r="F60" s="3">
-        <v>98700</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>98500</v>
+      </c>
+      <c r="G60" s="3">
+        <v>59900</v>
+      </c>
+      <c r="H60" s="3">
+        <v>56600</v>
+      </c>
+      <c r="I60" s="3">
+        <v>36600</v>
+      </c>
+      <c r="J60" s="3">
+        <v>29800</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2274,25 +2274,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>115300</v>
+        <v>132300</v>
       </c>
       <c r="E61" s="3">
-        <v>142900</v>
+        <v>150400</v>
       </c>
       <c r="F61" s="3">
-        <v>123100</v>
+        <v>122900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>14300</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>16900</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2307,25 +2307,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>37500</v>
+        <v>28900</v>
       </c>
       <c r="E62" s="3">
-        <v>30600</v>
+        <v>28200</v>
       </c>
       <c r="F62" s="3">
         <v>7000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="G62" s="3">
+        <v>200</v>
+      </c>
+      <c r="H62" s="3">
+        <v>600</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1500</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2439,25 +2439,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>234700</v>
+        <v>269100</v>
       </c>
       <c r="E66" s="3">
-        <v>304600</v>
+        <v>320600</v>
       </c>
       <c r="F66" s="3">
-        <v>228800</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>228500</v>
+      </c>
+      <c r="G66" s="3">
+        <v>74400</v>
+      </c>
+      <c r="H66" s="3">
+        <v>74100</v>
+      </c>
+      <c r="I66" s="3">
+        <v>44700</v>
+      </c>
+      <c r="J66" s="3">
+        <v>42200</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2619,25 +2619,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>95000</v>
+        <v>73000</v>
       </c>
       <c r="E72" s="3">
-        <v>76400</v>
+        <v>41900</v>
       </c>
       <c r="F72" s="3">
-        <v>24500</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>22600</v>
+      </c>
+      <c r="G72" s="3">
+        <v>21000</v>
+      </c>
+      <c r="H72" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I72" s="3">
+        <v>22600</v>
+      </c>
+      <c r="J72" s="3">
+        <v>15900</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2751,25 +2751,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>253600</v>
+        <v>290800</v>
       </c>
       <c r="E76" s="3">
-        <v>235100</v>
+        <v>247400</v>
       </c>
       <c r="F76" s="3">
-        <v>195800</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>195500</v>
+      </c>
+      <c r="G76" s="3">
+        <v>38200</v>
+      </c>
+      <c r="H76" s="3">
+        <v>27300</v>
+      </c>
+      <c r="I76" s="3">
+        <v>30900</v>
+      </c>
+      <c r="J76" s="3">
+        <v>24700</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2830,17 +2830,17 @@
       <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="G80" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H80" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I80" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J80" s="2">
+        <v>43100</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2855,25 +2855,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>23800</v>
+        <v>27300</v>
       </c>
       <c r="E81" s="3">
-        <v>17200</v>
+        <v>18100</v>
       </c>
       <c r="F81" s="3">
         <v>22600</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+      <c r="G81" s="3">
+        <v>24600</v>
+      </c>
+      <c r="H81" s="3">
+        <v>14100</v>
+      </c>
+      <c r="I81" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>8700</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2903,19 +2903,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>16800</v>
+        <v>9200</v>
       </c>
       <c r="E83" s="3">
-        <v>17000</v>
+        <v>9200</v>
       </c>
       <c r="F83" s="3">
         <v>8700</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H83" s="3">
+        <v>5700</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -3101,25 +3101,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>53100</v>
+        <v>60800</v>
       </c>
       <c r="E89" s="3">
-        <v>6500</v>
+        <v>6800</v>
       </c>
       <c r="F89" s="3">
-        <v>23600</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>23500</v>
+      </c>
+      <c r="G89" s="3">
+        <v>19400</v>
+      </c>
+      <c r="H89" s="3">
+        <v>22700</v>
+      </c>
+      <c r="I89" s="3">
+        <v>18700</v>
+      </c>
+      <c r="J89" s="3">
+        <v>5400</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3149,25 +3149,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-3700</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-5200</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-4100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-4900</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3248,25 +3248,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>11900</v>
+        <v>13600</v>
       </c>
       <c r="E94" s="3">
-        <v>-14800</v>
+        <v>-15600</v>
       </c>
       <c r="F94" s="3">
-        <v>-270700</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-270400</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-6700</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3302,13 +3302,13 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-22700</v>
+        <v>22600</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -3428,25 +3428,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-59900</v>
+        <v>-68700</v>
       </c>
       <c r="E100" s="3">
-        <v>18100</v>
+        <v>19000</v>
       </c>
       <c r="F100" s="3">
-        <v>247400</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>247100</v>
+      </c>
+      <c r="G100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-300</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3461,25 +3461,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="E101" s="3">
         <v>-800</v>
       </c>
       <c r="F101" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>-3800</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-700</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3494,25 +3494,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>4700</v>
+        <v>5300</v>
       </c>
       <c r="E102" s="3">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="F102" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>-3500</v>
+      </c>
+      <c r="G102" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H102" s="3">
+        <v>900</v>
+      </c>
+      <c r="I102" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-2400</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -656,160 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>382800</v>
+      </c>
+      <c r="E8" s="3">
         <v>460300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>413800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>259200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>184200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>168500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>152000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>136600</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>251600</v>
+      </c>
+      <c r="E9" s="3">
         <v>306600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>269600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>167900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>115700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>111700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>97700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>94900</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>131200</v>
+      </c>
+      <c r="E10" s="3">
         <v>153700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>144200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>91300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>68500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>56800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>54300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>41700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,41 +835,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>400</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
       <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4600</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,9 +904,12 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -900,12 +919,12 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>3900</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,30 +940,33 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E15" s="3">
         <v>13700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2100</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
@@ -954,9 +976,12 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +992,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>334200</v>
+      </c>
+      <c r="E17" s="3">
         <v>401500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>362000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>211400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>144100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>145600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>128000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>123300</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E18" s="3">
         <v>58800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>51800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>47800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>40100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>22800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>24000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13200</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,29 +1080,30 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,141 +1113,156 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>63300</v>
+      </c>
+      <c r="E21" s="3">
         <v>72000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>62100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>54900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>44300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>24800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>24000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13200</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E22" s="3">
         <v>17200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2000</v>
       </c>
       <c r="H22" s="3">
         <v>2000</v>
       </c>
       <c r="I22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E23" s="3">
         <v>43100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>37900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>37800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>37100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13100</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E24" s="3">
         <v>15800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4300</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1293,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E26" s="3">
         <v>27300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>18100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>22600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>24600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8800</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E27" s="3">
         <v>27300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>18100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>22600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>24600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>15300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8700</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1437,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,30 +1509,33 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1476,42 +1545,48 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E33" s="3">
         <v>27300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>18100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>22600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>24600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8700</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1617,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E35" s="3">
         <v>27300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>18100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>22600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>24600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8700</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,56 +1729,60 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E41" s="3">
         <v>43600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>24400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>31400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12400</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>18200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>143400</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -1703,48 +1792,54 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>123600</v>
+      </c>
+      <c r="E43" s="3">
         <v>136200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>139900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>87100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>48100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>41600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>39600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>35900</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1769,81 +1864,90 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E45" s="3">
         <v>7600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E46" s="3">
         <v>188000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>202600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>260400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>83700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>63500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>59800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>48400</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1862,87 +1966,96 @@
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>1300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1600</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E48" s="3">
         <v>16100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>309600</v>
+      </c>
+      <c r="E49" s="3">
         <v>344100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>332200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>132600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8000</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,42 +2122,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E52" s="3">
         <v>7900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1600</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1700</v>
       </c>
       <c r="H52" s="3">
         <v>1700</v>
       </c>
       <c r="I52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J52" s="3">
         <v>2200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2194,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>527000</v>
+      </c>
+      <c r="E54" s="3">
         <v>559900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>568000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>424000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>112700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>101400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>76500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>67400</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,206 +2265,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E57" s="3">
         <v>4500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E58" s="3">
         <v>26900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>48700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>33300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4900</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E59" s="3">
         <v>18800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>31100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9500</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>125100</v>
+      </c>
+      <c r="E60" s="3">
         <v>93800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>138100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>98500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>59900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>56600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>36600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29800</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E61" s="3">
         <v>132300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>150400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>122900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E62" s="3">
         <v>28900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>28200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1500</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2586,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>246600</v>
+      </c>
+      <c r="E66" s="3">
         <v>269100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>320600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>228500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>74400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>74100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>44700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>42200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2782,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>83300</v>
+      </c>
+      <c r="E72" s="3">
         <v>73000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>41900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>22600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2926,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>280400</v>
+      </c>
+      <c r="E76" s="3">
         <v>290800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>247400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>195500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>38200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>27300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>30900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24700</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +2998,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E81" s="3">
         <v>27300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>18100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>22600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>24600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8700</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,29 +3094,30 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>9200</v>
+        <v>8200</v>
       </c>
       <c r="E83" s="3">
         <v>9200</v>
       </c>
       <c r="F83" s="3">
+        <v>9200</v>
+      </c>
+      <c r="G83" s="3">
         <v>8700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5700</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,9 +3127,12 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3307,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>60500</v>
+      </c>
+      <c r="E89" s="3">
         <v>60800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>19400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>22700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>18700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3362,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4900</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3467,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E94" s="3">
         <v>13600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-270400</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-4100</v>
       </c>
       <c r="H94" s="3">
         <v>-4100</v>
       </c>
       <c r="I94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="J94" s="3">
         <v>-2200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6700</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,8 +3522,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3302,17 +3535,17 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>22600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>6000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>10000</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -3322,9 +3555,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,106 +3663,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-68700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>19000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>247100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-17300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E102" s="3">
         <v>5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2400</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
@@ -662,7 +662,9 @@
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -688,7 +690,7 @@
         <v>45291</v>
       </c>
       <c r="F7" s="2">
-        <v>44926</v>
+        <v>44927</v>
       </c>
       <c r="G7" s="2">
         <v>44561</v>
@@ -718,13 +720,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>382800</v>
+        <v>439000</v>
       </c>
       <c r="E8" s="3">
-        <v>460300</v>
+        <v>446900</v>
       </c>
       <c r="F8" s="3">
-        <v>413800</v>
+        <v>424100</v>
       </c>
       <c r="G8" s="3">
         <v>259200</v>
@@ -754,13 +756,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>251600</v>
+        <v>288700</v>
       </c>
       <c r="E9" s="3">
-        <v>306600</v>
+        <v>297700</v>
       </c>
       <c r="F9" s="3">
-        <v>269600</v>
+        <v>276300</v>
       </c>
       <c r="G9" s="3">
         <v>167900</v>
@@ -790,13 +792,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>131200</v>
+        <v>150200</v>
       </c>
       <c r="E10" s="3">
-        <v>153700</v>
+        <v>149200</v>
       </c>
       <c r="F10" s="3">
-        <v>144200</v>
+        <v>147800</v>
       </c>
       <c r="G10" s="3">
         <v>91300</v>
@@ -844,11 +846,11 @@
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
-        <v>500</v>
-      </c>
-      <c r="F12" s="3">
-        <v>400</v>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G12" s="3">
         <v>0</v>
@@ -950,13 +952,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>14600</v>
+        <v>10800</v>
       </c>
       <c r="E15" s="3">
-        <v>13700</v>
+        <v>13300</v>
       </c>
       <c r="F15" s="3">
-        <v>12200</v>
+        <v>18400</v>
       </c>
       <c r="G15" s="3">
         <v>8700</v>
@@ -999,13 +1001,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>334200</v>
+        <v>383400</v>
       </c>
       <c r="E17" s="3">
-        <v>401500</v>
+        <v>390000</v>
       </c>
       <c r="F17" s="3">
-        <v>362000</v>
+        <v>371100</v>
       </c>
       <c r="G17" s="3">
         <v>211400</v>
@@ -1035,13 +1037,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>48700</v>
+        <v>55600</v>
       </c>
       <c r="E18" s="3">
-        <v>58800</v>
+        <v>57000</v>
       </c>
       <c r="F18" s="3">
-        <v>51800</v>
+        <v>53000</v>
       </c>
       <c r="G18" s="3">
         <v>47800</v>
@@ -1086,14 +1088,14 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>15500</v>
       </c>
       <c r="E20" s="3">
-        <v>400</v>
+        <v>16600</v>
       </c>
       <c r="F20" s="3">
-        <v>1800</v>
+        <v>14400</v>
       </c>
       <c r="G20" s="3">
         <v>1600</v>
@@ -1123,13 +1125,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>63300</v>
+        <v>50900</v>
       </c>
       <c r="E21" s="3">
-        <v>72000</v>
+        <v>53600</v>
       </c>
       <c r="F21" s="3">
-        <v>62100</v>
+        <v>57000</v>
       </c>
       <c r="G21" s="3">
         <v>54900</v>
@@ -1159,13 +1161,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>23600</v>
+        <v>700</v>
       </c>
       <c r="E22" s="3">
-        <v>17200</v>
+        <v>1000</v>
       </c>
       <c r="F22" s="3">
-        <v>14000</v>
+        <v>1700</v>
       </c>
       <c r="G22" s="3">
         <v>5300</v>
@@ -1195,13 +1197,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>38200</v>
+        <v>43800</v>
       </c>
       <c r="E23" s="3">
-        <v>43100</v>
+        <v>41700</v>
       </c>
       <c r="F23" s="3">
-        <v>37900</v>
+        <v>38800</v>
       </c>
       <c r="G23" s="3">
         <v>37800</v>
@@ -1231,13 +1233,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>12200</v>
+        <v>14300</v>
       </c>
       <c r="E24" s="3">
-        <v>15800</v>
+        <v>15300</v>
       </c>
       <c r="F24" s="3">
-        <v>19800</v>
+        <v>20100</v>
       </c>
       <c r="G24" s="3">
         <v>15200</v>
@@ -1303,13 +1305,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>26100</v>
+        <v>29500</v>
       </c>
       <c r="E26" s="3">
-        <v>27300</v>
+        <v>26400</v>
       </c>
       <c r="F26" s="3">
-        <v>18100</v>
+        <v>18700</v>
       </c>
       <c r="G26" s="3">
         <v>22600</v>
@@ -1339,13 +1341,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>26100</v>
+        <v>29500</v>
       </c>
       <c r="E27" s="3">
-        <v>27300</v>
+        <v>26400</v>
       </c>
       <c r="F27" s="3">
-        <v>18100</v>
+        <v>18700</v>
       </c>
       <c r="G27" s="3">
         <v>22600</v>
@@ -1518,14 +1520,14 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-15500</v>
       </c>
       <c r="E32" s="3">
-        <v>-400</v>
+        <v>-16600</v>
       </c>
       <c r="F32" s="3">
-        <v>-1800</v>
+        <v>-14400</v>
       </c>
       <c r="G32" s="3">
         <v>-1600</v>
@@ -1555,13 +1557,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>26100</v>
+        <v>29500</v>
       </c>
       <c r="E33" s="3">
-        <v>27300</v>
+        <v>26400</v>
       </c>
       <c r="F33" s="3">
-        <v>18100</v>
+        <v>18700</v>
       </c>
       <c r="G33" s="3">
         <v>22600</v>
@@ -1627,13 +1629,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>26100</v>
+        <v>29500</v>
       </c>
       <c r="E35" s="3">
-        <v>27300</v>
+        <v>26400</v>
       </c>
       <c r="F35" s="3">
-        <v>18100</v>
+        <v>18700</v>
       </c>
       <c r="G35" s="3">
         <v>22600</v>
@@ -1674,7 +1676,7 @@
         <v>45291</v>
       </c>
       <c r="F38" s="2">
-        <v>44926</v>
+        <v>44927</v>
       </c>
       <c r="G38" s="2">
         <v>44561</v>
@@ -1736,13 +1738,13 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>56700</v>
+        <v>56600</v>
       </c>
       <c r="E41" s="3">
-        <v>43600</v>
+        <v>43700</v>
       </c>
       <c r="F41" s="3">
-        <v>35100</v>
+        <v>35600</v>
       </c>
       <c r="G41" s="3">
         <v>24400</v>
@@ -1772,13 +1774,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E42" s="3">
-        <v>700</v>
+        <v>2600</v>
       </c>
       <c r="F42" s="3">
-        <v>18200</v>
+        <v>20600</v>
       </c>
       <c r="G42" s="3">
         <v>143400</v>
@@ -1808,13 +1810,13 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>123600</v>
+        <v>123500</v>
       </c>
       <c r="E43" s="3">
-        <v>136200</v>
+        <v>136500</v>
       </c>
       <c r="F43" s="3">
-        <v>139900</v>
+        <v>141800</v>
       </c>
       <c r="G43" s="3">
         <v>87100</v>
@@ -1880,13 +1882,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7400</v>
+        <v>6700</v>
       </c>
       <c r="E45" s="3">
-        <v>7600</v>
+        <v>5600</v>
       </c>
       <c r="F45" s="3">
-        <v>9400</v>
+        <v>7300</v>
       </c>
       <c r="G45" s="3">
         <v>5500</v>
@@ -1916,13 +1918,13 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>192000</v>
+        <v>191800</v>
       </c>
       <c r="E46" s="3">
-        <v>188000</v>
+        <v>188400</v>
       </c>
       <c r="F46" s="3">
-        <v>202600</v>
+        <v>205300</v>
       </c>
       <c r="G46" s="3">
         <v>260400</v>
@@ -1991,10 +1993,10 @@
         <v>14000</v>
       </c>
       <c r="E48" s="3">
-        <v>16100</v>
+        <v>16200</v>
       </c>
       <c r="F48" s="3">
-        <v>21100</v>
+        <v>21400</v>
       </c>
       <c r="G48" s="3">
         <v>23600</v>
@@ -2024,13 +2026,13 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>309600</v>
+        <v>309300</v>
       </c>
       <c r="E49" s="3">
-        <v>344100</v>
+        <v>344900</v>
       </c>
       <c r="F49" s="3">
-        <v>332200</v>
+        <v>336500</v>
       </c>
       <c r="G49" s="3">
         <v>132600</v>
@@ -2138,7 +2140,7 @@
         <v>7900</v>
       </c>
       <c r="F52" s="3">
-        <v>9200</v>
+        <v>9300</v>
       </c>
       <c r="G52" s="3">
         <v>1600</v>
@@ -2204,13 +2206,13 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>527000</v>
+        <v>526400</v>
       </c>
       <c r="E54" s="3">
-        <v>559900</v>
+        <v>561200</v>
       </c>
       <c r="F54" s="3">
-        <v>568000</v>
+        <v>575500</v>
       </c>
       <c r="G54" s="3">
         <v>424000</v>
@@ -2278,7 +2280,7 @@
         <v>4500</v>
       </c>
       <c r="F57" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="G57" s="3">
         <v>6000</v>
@@ -2308,13 +2310,13 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>50100</v>
+        <v>52500</v>
       </c>
       <c r="E58" s="3">
-        <v>26900</v>
+        <v>27000</v>
       </c>
       <c r="F58" s="3">
-        <v>48700</v>
+        <v>50200</v>
       </c>
       <c r="G58" s="3">
         <v>33300</v>
@@ -2344,13 +2346,13 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25600</v>
+        <v>23200</v>
       </c>
       <c r="E59" s="3">
-        <v>18800</v>
+        <v>22000</v>
       </c>
       <c r="F59" s="3">
-        <v>31100</v>
+        <v>33500</v>
       </c>
       <c r="G59" s="3">
         <v>16200</v>
@@ -2380,13 +2382,13 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>125100</v>
+        <v>125000</v>
       </c>
       <c r="E60" s="3">
-        <v>93800</v>
+        <v>94000</v>
       </c>
       <c r="F60" s="3">
-        <v>138100</v>
+        <v>139900</v>
       </c>
       <c r="G60" s="3">
         <v>98500</v>
@@ -2416,13 +2418,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>98200</v>
+        <v>98100</v>
       </c>
       <c r="E61" s="3">
-        <v>132300</v>
+        <v>132600</v>
       </c>
       <c r="F61" s="3">
-        <v>150400</v>
+        <v>152400</v>
       </c>
       <c r="G61" s="3">
         <v>122900</v>
@@ -2458,7 +2460,7 @@
         <v>28900</v>
       </c>
       <c r="F62" s="3">
-        <v>28200</v>
+        <v>28600</v>
       </c>
       <c r="G62" s="3">
         <v>7000</v>
@@ -2596,13 +2598,13 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>246600</v>
+        <v>246300</v>
       </c>
       <c r="E66" s="3">
-        <v>269100</v>
+        <v>269700</v>
       </c>
       <c r="F66" s="3">
-        <v>320600</v>
+        <v>324900</v>
       </c>
       <c r="G66" s="3">
         <v>228500</v>
@@ -2792,13 +2794,13 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>83300</v>
+        <v>97900</v>
       </c>
       <c r="E72" s="3">
-        <v>73000</v>
+        <v>68400</v>
       </c>
       <c r="F72" s="3">
-        <v>41900</v>
+        <v>42100</v>
       </c>
       <c r="G72" s="3">
         <v>22600</v>
@@ -2936,13 +2938,13 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>280400</v>
+        <v>280100</v>
       </c>
       <c r="E76" s="3">
-        <v>290800</v>
+        <v>291500</v>
       </c>
       <c r="F76" s="3">
-        <v>247400</v>
+        <v>250700</v>
       </c>
       <c r="G76" s="3">
         <v>195500</v>
@@ -3019,7 +3021,7 @@
         <v>45291</v>
       </c>
       <c r="F80" s="2">
-        <v>44926</v>
+        <v>44927</v>
       </c>
       <c r="G80" s="2">
         <v>44561</v>
@@ -3049,13 +3051,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>26100</v>
+        <v>29500</v>
       </c>
       <c r="E81" s="3">
-        <v>27300</v>
+        <v>26400</v>
       </c>
       <c r="F81" s="3">
-        <v>18100</v>
+        <v>18700</v>
       </c>
       <c r="G81" s="3">
         <v>22600</v>
@@ -3101,13 +3103,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8200</v>
+        <v>7800</v>
       </c>
       <c r="E83" s="3">
-        <v>9200</v>
+        <v>8900</v>
       </c>
       <c r="F83" s="3">
-        <v>9200</v>
+        <v>18400</v>
       </c>
       <c r="G83" s="3">
         <v>8700</v>
@@ -3317,13 +3319,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>60500</v>
+        <v>69000</v>
       </c>
       <c r="E89" s="3">
-        <v>60800</v>
+        <v>59300</v>
       </c>
       <c r="F89" s="3">
-        <v>6800</v>
+        <v>5400</v>
       </c>
       <c r="G89" s="3">
         <v>23500</v>
@@ -3369,13 +3371,13 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-9200</v>
+        <v>-10600</v>
       </c>
       <c r="E91" s="3">
-        <v>-5000</v>
+        <v>-4800</v>
       </c>
       <c r="F91" s="3">
-        <v>-3700</v>
+        <v>-4500</v>
       </c>
       <c r="G91" s="3">
         <v>-5200</v>
@@ -3477,13 +3479,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-8700</v>
+        <v>-9900</v>
       </c>
       <c r="E94" s="3">
-        <v>13600</v>
+        <v>13300</v>
       </c>
       <c r="F94" s="3">
-        <v>-15600</v>
+        <v>-16800</v>
       </c>
       <c r="G94" s="3">
         <v>-270400</v>
@@ -3673,13 +3675,13 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-33300</v>
+        <v>-36000</v>
       </c>
       <c r="E100" s="3">
-        <v>-68700</v>
+        <v>-67300</v>
       </c>
       <c r="F100" s="3">
-        <v>19000</v>
+        <v>18300</v>
       </c>
       <c r="G100" s="3">
         <v>247100</v>
@@ -3709,13 +3711,13 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>4000</v>
+        <v>-10200</v>
       </c>
       <c r="E101" s="3">
-        <v>-500</v>
+        <v>2800</v>
       </c>
       <c r="F101" s="3">
-        <v>-800</v>
+        <v>4400</v>
       </c>
       <c r="G101" s="3">
         <v>-3800</v>
@@ -3745,13 +3747,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>22500</v>
+        <v>12900</v>
       </c>
       <c r="E102" s="3">
-        <v>5300</v>
+        <v>8100</v>
       </c>
       <c r="F102" s="3">
-        <v>9500</v>
+        <v>11300</v>
       </c>
       <c r="G102" s="3">
         <v>-3500</v>

--- a/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CINT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -656,174 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>489700</v>
+      </c>
+      <c r="E8" s="3">
         <v>439000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>446900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>424100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>259200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>184200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>168500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>152000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>136600</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>333100</v>
+      </c>
+      <c r="E9" s="3">
         <v>288700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>297700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>276300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>167900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>115700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>111700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>97700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>94900</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>156600</v>
+      </c>
+      <c r="E10" s="3">
         <v>150200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>149200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>147800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>91300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>68500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>56800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>54300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>41700</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,8 +850,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -852,30 +865,33 @@
       <c r="F12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="3">
-        <v>0</v>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
         <v>700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4600</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -909,9 +925,12 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -924,12 +943,12 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>3900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -945,33 +964,36 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E15" s="3">
         <v>10800</v>
       </c>
-      <c r="E15" s="3">
-        <v>13300</v>
-      </c>
       <c r="F15" s="3">
+        <v>18700</v>
+      </c>
+      <c r="G15" s="3">
         <v>18400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2100</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -981,9 +1003,12 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -995,80 +1020,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>424100</v>
+      </c>
+      <c r="E17" s="3">
         <v>383400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>390000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>371100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>211400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>144100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>145600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>128000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>123300</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E18" s="3">
         <v>55600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>57000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>53000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>47800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>40100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>22800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>24000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13200</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1083,32 +1115,33 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>15500</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
-        <v>16600</v>
+        <v>700</v>
       </c>
       <c r="F20" s="3">
-        <v>14400</v>
+        <v>-400</v>
       </c>
       <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3">
         <v>1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1118,153 +1151,168 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>50900</v>
+        <v>76500</v>
       </c>
       <c r="E21" s="3">
-        <v>53600</v>
+        <v>65700</v>
       </c>
       <c r="F21" s="3">
-        <v>57000</v>
+        <v>76000</v>
       </c>
       <c r="G21" s="3">
+        <v>71300</v>
+      </c>
+      <c r="H21" s="3">
         <v>54900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>44300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>24800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>24000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13200</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>700</v>
+        <v>13500</v>
       </c>
       <c r="E22" s="3">
-        <v>1000</v>
+        <v>14700</v>
       </c>
       <c r="F22" s="3">
-        <v>1700</v>
+        <v>17700</v>
       </c>
       <c r="G22" s="3">
+        <v>16100</v>
+      </c>
+      <c r="H22" s="3">
         <v>5300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2000</v>
       </c>
       <c r="I22" s="3">
         <v>2000</v>
       </c>
       <c r="J22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K22" s="3">
         <v>1400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E23" s="3">
         <v>43800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>41700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>38800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>37800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>37100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13100</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E24" s="3">
         <v>14300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>15300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>20100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4300</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1298,81 +1346,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E26" s="3">
         <v>29500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>26400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>24600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8800</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E27" s="3">
         <v>29500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>26400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>22600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>24600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>14100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8700</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1406,9 +1463,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1442,9 +1502,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1478,9 +1541,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1514,33 +1580,36 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-15500</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
-        <v>-16600</v>
+        <v>-700</v>
       </c>
       <c r="F32" s="3">
-        <v>-14400</v>
+        <v>400</v>
       </c>
       <c r="G32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1550,45 +1619,51 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E33" s="3">
         <v>29500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>26400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>22600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>24600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8700</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1622,86 +1697,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E35" s="3">
         <v>29500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>26400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>22600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>24600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8700</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1716,8 +1800,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1732,62 +1817,66 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E41" s="3">
         <v>56600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>43700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>35600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>24400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>31400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12400</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>200</v>
+      </c>
+      <c r="E42" s="3">
         <v>700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>20600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>143400</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -1797,51 +1886,57 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>141700</v>
+      </c>
+      <c r="E43" s="3">
         <v>123500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>136500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>141800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>87100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>48100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>41600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>39600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>35900</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1869,87 +1964,96 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E45" s="3">
         <v>6700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>196100</v>
+      </c>
+      <c r="E46" s="3">
         <v>191800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>188400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>205300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>260400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>83700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>63500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>59800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>48400</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1971,93 +2075,102 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>1300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1600</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E48" s="3">
         <v>14000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>329300</v>
+      </c>
+      <c r="E49" s="3">
         <v>309300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>344900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>336500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>132600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2091,9 +2204,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2127,45 +2243,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E52" s="3">
         <v>10000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1700</v>
       </c>
       <c r="I52" s="3">
         <v>1700</v>
       </c>
       <c r="J52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K52" s="3">
         <v>2200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2199,45 +2321,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>550500</v>
+      </c>
+      <c r="E54" s="3">
         <v>526400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>561200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>575500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>424000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>112700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>101400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>76500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>67400</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2252,8 +2380,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2268,224 +2397,243 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E57" s="3">
         <v>4800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E58" s="3">
         <v>52500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>27000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>50200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>33300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4900</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>23200</v>
+        <v>9400</v>
       </c>
       <c r="E59" s="3">
+        <v>20100</v>
+      </c>
+      <c r="F59" s="3">
         <v>22000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>33500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9500</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>146900</v>
+      </c>
+      <c r="E60" s="3">
         <v>125000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>94000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>139900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>98500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>59900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>56600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>36600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29800</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>61100</v>
+      </c>
+      <c r="E61" s="3">
         <v>98100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>132600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>152400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>122900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E62" s="3">
         <v>6900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>28900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2519,9 +2667,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2555,9 +2706,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2591,45 +2745,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>241600</v>
+      </c>
+      <c r="E66" s="3">
         <v>246300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>269700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>324900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>228500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>74400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>74100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>44700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>42200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2644,8 +2804,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2679,9 +2840,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2715,9 +2879,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2751,9 +2918,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2787,45 +2957,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>138500</v>
+      </c>
+      <c r="E72" s="3">
         <v>97900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>68400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>42100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>22600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>21000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>22600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15900</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2859,9 +3035,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2895,9 +3074,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2931,45 +3113,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>308900</v>
+      </c>
+      <c r="E76" s="3">
         <v>280100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>291500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>250700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>195500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>38200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>30900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24700</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3003,86 +3191,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E81" s="3">
         <v>29500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>26400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>22600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>24600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8700</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3097,32 +3294,33 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E83" s="3">
         <v>7800</v>
       </c>
-      <c r="E83" s="3">
-        <v>8900</v>
-      </c>
       <c r="F83" s="3">
+        <v>18700</v>
+      </c>
+      <c r="G83" s="3">
         <v>18400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5700</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3132,9 +3330,12 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3168,9 +3369,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3204,9 +3408,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3240,9 +3447,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3276,9 +3486,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3312,45 +3525,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E89" s="3">
         <v>69000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>59300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>23500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>19400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>22700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3365,44 +3584,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4900</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3436,9 +3659,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3472,45 +3698,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>13300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-270400</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-4100</v>
       </c>
       <c r="I94" s="3">
         <v>-4100</v>
       </c>
       <c r="J94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6700</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3525,8 +3757,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3540,17 +3773,17 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>22600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>6000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>10000</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -3560,9 +3793,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3596,9 +3832,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3632,9 +3871,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3668,115 +3910,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-61100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-36000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-67300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>18300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>247100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-17300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-10200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E102" s="3">
         <v>12900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2400</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
